--- a/branches/readme-ballot/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
+++ b/branches/readme-ballot/StructureDefinition-mii-pr-labor-laboranforderung.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:49:53+00:00</t>
+    <t>2026-09-14T08:10:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
